--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.71869923646899</v>
+        <v>4.341788625926212</v>
       </c>
       <c r="D2" t="n">
-        <v>35.65525859358788</v>
+        <v>5.793979521458031</v>
       </c>
       <c r="E2" t="n">
-        <v>3.777558244945229</v>
+        <v>0.6138532148036</v>
       </c>
       <c r="F2" t="n">
-        <v>10.60442290150607</v>
+        <v>1.723218721494736</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.27381572635945</v>
+        <v>5.569495055533412</v>
       </c>
       <c r="D3" t="n">
-        <v>56.86410439660002</v>
+        <v>9.240416964447503</v>
       </c>
       <c r="E3" t="n">
-        <v>3.777558244945229</v>
+        <v>0.6138532148036</v>
       </c>
       <c r="F3" t="n">
-        <v>10.60442290150607</v>
+        <v>1.723218721494736</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
